--- a/config/settings.xlsx
+++ b/config/settings.xlsx
@@ -503,9 +503,7 @@
           <t>SAVINGS_TARGET_MONTHLY_INR</t>
         </is>
       </c>
-      <c r="C3" s="4" t="n">
-        <v>75000</v>
-      </c>
+      <c r="C3" s="4" t="n"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>whole number</t>

--- a/config/settings.xlsx
+++ b/config/settings.xlsx
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -493,25 +493,25 @@
       </c>
     </row>
     <row r="3" ht="29" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>Business targets</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SAVINGS_TARGET_MONTHLY_INR</t>
+          <t>TARGET_DISCOUNT_PCT</t>
         </is>
       </c>
       <c r="C3" s="4" t="n"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>whole number</t>
+          <t>percent 0-100 (12 = 12%)</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>Monthly savings ambition in Rs. Gate C6 reports MEETS/BELOW against this. A verdict only — a smaller plan still executes.</t>
+          <t>Headline discount % the brand is steering toward (dashboard KPI).</t>
         </is>
       </c>
     </row>
@@ -523,7 +523,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>TARGET_DISCOUNT_PCT</t>
+          <t>TARGET_WEIGHTED_DISCOUNT_PCT</t>
         </is>
       </c>
       <c r="C4" s="4" t="n"/>
@@ -534,7 +534,7 @@
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>Headline discount % the brand is steering toward (dashboard KPI).</t>
+          <t>Revenue-weighted portfolio discount % the flywheel glides toward.</t>
         </is>
       </c>
     </row>
@@ -546,18 +546,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>TARGET_WEIGHTED_DISCOUNT_PCT</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="n"/>
+          <t>TARGET_QUARTER</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Q4 2026</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>percent 0-100 (12 = 12%)</t>
+          <t>text</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>Revenue-weighted portfolio discount % the flywheel glides toward.</t>
+          <t>Quarter label the discount target is set for, e.g. Q4 2026.</t>
         </is>
       </c>
     </row>
@@ -569,22 +573,18 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>TARGET_QUARTER</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>Q4 2026</t>
-        </is>
-      </c>
+          <t>DEFAULT_BUDGET_PCT_CAP</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="n"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>fraction 0-1 (0.12 = 12%)</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>Quarter label the discount target is set for, e.g. Q4 2026.</t>
+          <t>Weekly discount-spend cap as a fraction of gross sales. 0.12 = 12%. Blocks reinvestment when breached; never forces extra cuts.</t>
         </is>
       </c>
     </row>
@@ -596,18 +596,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>DEFAULT_BUDGET_PCT_CAP</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="n"/>
+          <t>TARGET_TIMELINE_WEEKS</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>12</v>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>fraction 0-1 (0.12 = 12%)</t>
+          <t>whole number</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>Weekly discount-spend cap as a fraction of gross sales. 0.12 = 12%. Blocks reinvestment when breached; never forces extra cuts.</t>
+          <t>Every cell's full discount gap must close within this many weekly cycles.</t>
         </is>
       </c>
     </row>
@@ -619,57 +621,59 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>TARGET_TIMELINE_WEEKS</t>
+          <t>MIN_DISCOUNT_CHANGE_PPT</t>
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>whole number</t>
+          <t>number</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>Every cell's full discount gap must close within this many weekly cycles.</t>
+          <t>Smallest weekly discount step in percentage points. Gaps smaller than this close in one cycle.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Business targets</t>
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Brand identity</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>MIN_DISCOUNT_CHANGE_PPT</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="n">
-        <v>3</v>
+          <t>BRAND_NAME</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Epigamia</t>
+        </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>text</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>Smallest weekly discount step in percentage points. Gaps smaller than this close in one cycle.</t>
+          <t>The client's own brand as it appears on the platform.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>Brand identity</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>BRAND_NAME</t>
+          <t>OWN_BRAND_PATTERNS</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -679,12 +683,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>list, separate with |</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>The client's own brand as it appears on the platform.</t>
+          <t>Every spelling of the own brand in the data. Blank = derive from BRAND_NAME. Ingestion fails loud if these match no rows, or match a competitor too.</t>
         </is>
       </c>
     </row>
@@ -696,22 +700,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>OWN_BRAND_PATTERNS</t>
+          <t>PLATFORM_NAME</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Epigamia</t>
+          <t>Blinkit</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>list, separate with |</t>
+          <t>text</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>Every spelling of the own brand in the data. Blank = derive from BRAND_NAME. Ingestion fails loud if these match no rows, or match a competitor too.</t>
+          <t>The quick-commerce platform, e.g. Blinkit.</t>
         </is>
       </c>
     </row>
@@ -723,22 +727,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>PLATFORM_NAME</t>
+          <t>STRATEGIC_SKUS</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Blinkit</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>list of ids, separate with |</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>The quick-commerce platform, e.g. Blinkit.</t>
+          <t>Hero PRODUCT_IDs that must NEVER be auto-cut, whatever the model says. Separate with |. Write none for no hero protection.</t>
         </is>
       </c>
     </row>
@@ -750,22 +754,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>STRATEGIC_SKUS</t>
+          <t>COMPETITOR_BRANDS</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>Mother Dairy | Amul | Milky Mist</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>list of ids, separate with |</t>
+          <t>list, separate with |</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>Hero PRODUCT_IDs that must NEVER be auto-cut, whatever the model says. Separate with |. Write none for no hero protection.</t>
+          <t>Competitor brand names (max 3, exactly as spelled in the platform export) used to build the relative-price index that controls the demand model. Separate with |. Default: Organic Tattva.</t>
         </is>
       </c>
     </row>
@@ -777,65 +781,63 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>COMPETITOR_BRANDS</t>
+          <t>STRICT_OWN_BRAND_MATCH</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Mother Dairy | Amul | Milky Mist</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>list, separate with |</t>
+          <t>yes / no</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>Competitor brand names (max 3, exactly as spelled in the platform export) used to build the relative-price index that controls the demand model. Separate with |. Default: Organic Tattva.</t>
+          <t>yes = fail loudly if the brand patterns also match a competitor brand (e.g. 'Sun' catching 'Sunfeast'). Keep yes unless you truly own several distinct brand strings.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="29" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Brand identity</t>
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Cost structure</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>STRICT_OWN_BRAND_MATCH</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
+          <t>DEFAULT_COGS_PCT</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="n">
+        <v>0.5</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>yes / no</t>
+          <t>fraction 0-1 (0.12 = 12%)</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>yes = fail loudly if the brand patterns also match a competitor brand (e.g. 'Sun' catching 'Sunfeast'). Keep yes unless you truly own several distinct brand strings.</t>
+          <t>Cost of goods as a fraction of MRP. 0.50 = 50%. PROXY until finance supplies real per-SKU costs — every profit figure inherits this.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="29" customHeight="1">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Cost structure</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>DEFAULT_COGS_PCT</t>
+          <t>DEFAULT_COMMISSION_PCT</t>
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -844,7 +846,7 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>Cost of goods as a fraction of MRP. 0.50 = 50%. PROXY until finance supplies real per-SKU costs — every profit figure inherits this.</t>
+          <t>Platform commission as a fraction of selling price. 0.15 = 15%.</t>
         </is>
       </c>
     </row>
@@ -856,70 +858,70 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>DEFAULT_COMMISSION_PCT</t>
+          <t>DEFAULT_FULFILLMENT_FEE</t>
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.15</v>
+        <v>10</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>fraction 0-1 (0.12 = 12%)</t>
+          <t>number</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>Platform commission as a fraction of selling price. 0.15 = 15%.</t>
+          <t>Fulfilment cost in Rs per unit.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Cost structure</t>
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Model and guardrails</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>DEFAULT_FULFILLMENT_FEE</t>
+          <t>TRAIN_LOOKBACK_DAYS</t>
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>10</v>
+        <v>180</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>whole number</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>Train only on the last N days of regular trading. The single biggest accuracy lever — shorter avoids stale price regimes and launch ramps.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="29" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Model and guardrails</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>OUTLIER_Z_THRESHOLD</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
           <t>number</t>
         </is>
       </c>
-      <c r="E18" s="5" t="inlineStr">
-        <is>
-          <t>Fulfilment cost in Rs per unit.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="29" customHeight="1">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>Model and guardrails</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>TRAIN_LOOKBACK_DAYS</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="n">
-        <v>180</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>whole number</t>
-        </is>
-      </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>Train only on the last N days of regular trading. The single biggest accuracy lever — shorter avoids stale price regimes and launch ramps.</t>
+          <t>Per-cell z-score above which a day is treated as an outlier and excluded from training. 2.0 is the tuned production value; 3.0 keeps more days.</t>
         </is>
       </c>
     </row>
@@ -931,11 +933,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>OUTLIER_Z_THRESHOLD</t>
+          <t>MARGINAL_ROI_THRESHOLD</t>
         </is>
       </c>
       <c r="C20" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -944,7 +946,7 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>Per-cell z-score above which a day is treated as an outlier and excluded from training. 2.0 is the tuned production value; 3.0 keeps more days.</t>
+          <t>The elbow: deepest discount whose marginal ROI still clears this. 1.0 = the last rupee of discount must at least pay for itself.</t>
         </is>
       </c>
     </row>
@@ -956,11 +958,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>MARGINAL_ROI_THRESHOLD</t>
+          <t>HISTORICAL_FLOOR_PERCENTILE</t>
         </is>
       </c>
       <c r="C21" s="4" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -969,7 +971,7 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>The elbow: deepest discount whose marginal ROI still clears this. 1.0 = the last rupee of discount must at least pay for itself.</t>
+          <t>Percentile of a cell's own recent discounts treated as its proven-safe floor. 25 = 'we ran this low on a quarter of days and survived'.</t>
         </is>
       </c>
     </row>
@@ -981,11 +983,11 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>HISTORICAL_FLOOR_PERCENTILE</t>
+          <t>INELASTIC_ELASTICITY_THRESHOLD</t>
         </is>
       </c>
       <c r="C22" s="4" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -994,7 +996,7 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>Percentile of a cell's own recent discounts treated as its proven-safe floor. 25 = 'we ran this low on a quarter of days and survived'.</t>
+          <t>Cells with |elasticity| at or below this cannot pay for a discount; they are held/raised, never reinvested. 1.0 is the theorem boundary.</t>
         </is>
       </c>
     </row>
@@ -1006,20 +1008,20 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>INELASTIC_ELASTICITY_THRESHOLD</t>
+          <t>REINVEST_MIN_VOL_LIFT_PCT</t>
         </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>percent 0-100 (12 = 12%)</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>Cells with |elasticity| at or below this cannot pay for a discount; they are held/raised, never reinvested. 1.0 is the theorem boundary.</t>
+          <t>A reinvest candidate must lift volume by at least this %, net of leakage.</t>
         </is>
       </c>
     </row>
@@ -1031,11 +1033,11 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>REINVEST_MIN_VOL_LIFT_PCT</t>
+          <t>REINVEST_MAX_MARGIN_SAC_PCT</t>
         </is>
       </c>
       <c r="C24" s="4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1044,7 +1046,7 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>A reinvest candidate must lift volume by at least this %, net of leakage.</t>
+          <t>A reinvest candidate may sacrifice at most this % of current contribution.</t>
         </is>
       </c>
     </row>
@@ -1056,20 +1058,20 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>REINVEST_MAX_MARGIN_SAC_PCT</t>
+          <t>REINVEST_MIN_ELASTICITY</t>
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>percent 0-100 (12 = 12%)</t>
+          <t>number</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>A reinvest candidate may sacrifice at most this % of current contribution.</t>
+          <t>|elasticity| a cell needs before deeper discount is even considered.</t>
         </is>
       </c>
     </row>
@@ -1081,20 +1083,20 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>REINVEST_MIN_ELASTICITY</t>
+          <t>VOLUME_DROP_TOLERANCE_PCT</t>
         </is>
       </c>
       <c r="C26" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>percent 0-100 (12 = 12%)</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>|elasticity| a cell needs before deeper discount is even considered.</t>
+          <t>Kill-switch: a cell strikes when actual volume misses prediction by more than this %. Two strikes revert the cut.</t>
         </is>
       </c>
     </row>
@@ -1106,43 +1108,18 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>VOLUME_DROP_TOLERANCE_PCT</t>
+          <t>DRIFT_ALERT_THRESHOLD</t>
         </is>
       </c>
       <c r="C27" s="4" t="n">
-        <v>5</v>
+        <v>0.15</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>percent 0-100 (12 = 12%)</t>
+          <t>fraction 0-1 (0.12 = 12%)</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
-        <is>
-          <t>Kill-switch: a cell strikes when actual volume misses prediction by more than this %. Two strikes revert the cut.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Model and guardrails</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>DRIFT_ALERT_THRESHOLD</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>fraction 0-1 (0.12 = 12%)</t>
-        </is>
-      </c>
-      <c r="E28" s="5" t="inlineStr">
         <is>
           <t>Prediction error fraction that counts as model drift. 0.15 = 15%.</t>
         </is>
